--- a/greenlife_scraper/resumo_macro.xlsx
+++ b/greenlife_scraper/resumo_macro.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1024,6 +1024,32 @@
         <v>1269</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
